--- a/files/2026-09-07/RTL_vs_competitors_price_diff_2026-09-07.xlsx
+++ b/files/2026-09-07/RTL_vs_competitors_price_diff_2026-09-07.xlsx
@@ -166,6 +166,492 @@
     <t xml:space="preserve">Froza</t>
   </si>
   <si>
+    <t xml:space="preserve">39071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Febi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6248.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5763.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-485.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6248.85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8500000000003638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6163.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 5 763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550061548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes-Benz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3400.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3430.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2973.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-427.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 427 руб. (12.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-12.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989320911ABDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1637.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1867.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1065.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-572.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1184.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-452.29999999999995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 572 руб. (34.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-34.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989440411FULW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1741.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1985.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1436.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-305.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">911 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1495.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-245.58999999999992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2035.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 305 руб. (17.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989671011FBDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1206.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1375.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1212.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1169 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1112.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-93.90000000000009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 94 руб. (7.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 1 112.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-93.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989681013FSEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4948.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5641.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4561.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-387.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4510.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-438.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 438 руб. (8.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STparts 4 510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691011FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1223.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1395.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1008.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-215.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1402 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1045.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-178.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 215 руб. (17.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 1 008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A000989691013FSDW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5329.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6076.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4806.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-523.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1776 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4994.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-335.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 523 руб. (9.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 4 806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM10038-4EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mazda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3240.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3694.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2775.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-465.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2860.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-380.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 465 руб. (14.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitsubishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2729.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3112.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2337.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-392.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">277 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2585.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 392 руб. (14.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 2 337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MZ320101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3803.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4211.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3197.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-606.8000000000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">256 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3323.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-480.8000000000002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 607 руб. (16.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 3 197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-606.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT5QMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">768.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">877.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-40.52999999999997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">672 шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">740.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-28.24000000000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-625.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дороже мин. на 41 руб. (5.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATS 728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-40.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">08886-81875</t>
   </si>
   <si>
@@ -181,18 +667,12 @@
     <t xml:space="preserve">5355.0</t>
   </si>
   <si>
-    <t xml:space="preserve">4561.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">-136.0</t>
   </si>
   <si>
     <t xml:space="preserve">1665 шт</t>
   </si>
   <si>
-    <t xml:space="preserve">4510.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">-187.0</t>
   </si>
   <si>
@@ -205,16 +685,10 @@
     <t xml:space="preserve">255 шт</t>
   </si>
   <si>
-    <t xml:space="preserve">143.35</t>
-  </si>
-  <si>
     <t xml:space="preserve">-4553.65</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 187 руб. (4.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 4 510</t>
+    <t xml:space="preserve">конкурент ниже на 187 руб. (4.0%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">-4.0</t>
@@ -265,7 +739,7 @@
     <t xml:space="preserve">852.2600000000002</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 179 руб. (4.2%)</t>
+    <t xml:space="preserve">конкурент ниже на 179 руб. (4.2%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 4 113.59</t>
@@ -277,57 +751,12 @@
     <t xml:space="preserve">-4.2</t>
   </si>
   <si>
-    <t xml:space="preserve">39071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Febi DSG, для робот. КПП с двойным сцеплением, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Febi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6248.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5763.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-485.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6248.85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8500000000003638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6163.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 485 руб. (7.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 5 763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.8</t>
-  </si>
-  <si>
     <t xml:space="preserve">4024610</t>
   </si>
   <si>
     <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Япония), (4л)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mitsubishi</t>
-  </si>
-  <si>
     <t xml:space="preserve">98</t>
   </si>
   <si>
@@ -364,7 +793,7 @@
     <t xml:space="preserve">-3377.25</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 78 руб. (2.2%)</t>
+    <t xml:space="preserve">конкурент ниже на 78 руб. (2.2%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 3 443</t>
@@ -376,39 +805,6 @@
     <t xml:space="preserve">-2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">550061548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Shell Helix Ultra X SP 0W-30 (A3/B4), MB 229.5/226.5, (Оман), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercedes-Benz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3400.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3430.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2973.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-427.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 427 руб. (12.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-12.6</t>
-  </si>
-  <si>
     <t xml:space="preserve">83215A1C740</t>
   </si>
   <si>
@@ -430,7 +826,7 @@
     <t xml:space="preserve">-70.69000000000005</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 71 руб. (3.6%)</t>
+    <t xml:space="preserve">конкурент ниже на 71 руб. (3.6%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 914</t>
@@ -442,42 +838,6 @@
     <t xml:space="preserve">-3.6</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989320911ABDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, бензин/дизель, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1637.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1867.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1065.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-572.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1184.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-452.29999999999995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 572 руб. (34.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-34.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">A000989440411FDNE</t>
   </si>
   <si>
@@ -499,7 +859,7 @@
     <t xml:space="preserve">-12.1099999999999</t>
   </si>
   <si>
-    <t xml:space="preserve">дороже мин. на 12 руб. (0.7%)</t>
+    <t xml:space="preserve">конкурент ниже на 12 руб. (0.7%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">STparts 1 627.89</t>
@@ -511,93 +871,6 @@
     <t xml:space="preserve">-0.7</t>
   </si>
   <si>
-    <t xml:space="preserve">A000989440411FULW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mercedes-Benz ATF MB 236.15, (Бельгия), (1л.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1741.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1985.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1436.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-305.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">911 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1495.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-245.58999999999992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2035.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 305 руб. (17.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989671011FBDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.52, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1206.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1375.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1212.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1169 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1112.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-93.90000000000009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 94 руб. (7.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STparts 1 112.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-93.9</t>
-  </si>
-  <si>
     <t xml:space="preserve">A000989681011FSEW</t>
   </si>
   <si>
@@ -634,286 +907,13 @@
     <t xml:space="preserve">217.0</t>
   </si>
   <si>
-    <t xml:space="preserve">256 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 37 руб. (3.9%)</t>
+    <t xml:space="preserve">конкурент ниже на 37 руб. (3.9%) · зона торга ≤5%</t>
   </si>
   <si>
     <t xml:space="preserve">ATS 911</t>
   </si>
   <si>
     <t xml:space="preserve">-3.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989681013FSEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-40 / MB 229.5 (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4948.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5641.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-387.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">737 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-438.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 438 руб. (8.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691011FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (1л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1223.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1395.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1008.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-215.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1402 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1045.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-178.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 215 руб. (17.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 1 008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A000989691013FSDW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mercedes-Benz 5W-30 / MB 229.51, (Германия), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5329.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6076.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4806.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-523.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1776 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4994.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-335.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 523 руб. (9.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 4 806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM10038-4EN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Моторное масло Mazda "GOLDEN" SN 5W-30 / ILSAC GF-5, для бенз. двигателей, (Дубай), (4л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mazda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3240.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3694.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2775.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-465.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2860.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-380.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 465 руб. (14.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Таиланд), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2729.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3112.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2337.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-392.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">277 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2585.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 392 руб. (14.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 2 337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MZ320101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Mitsubishi ATF SP-III, для АКПП и ГУР, (Дубай), (5л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3803.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4211.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3197.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-606.8000000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3323.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-480.8000000000002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 607 руб. (16.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 3 197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-606.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XT5QMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Трансмиссионное масло Ford Motorcraft ATF Mercon V, для АКПП / ГУР (красный), (США), (0,946л)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">877.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">728.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-40.52999999999997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">672 шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">740.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-28.24000000000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-625.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">дороже мин. на 41 руб. (5.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATS 728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-40.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.3</t>
   </si>
   <si>
     <t xml:space="preserve">08234P99F4PY1</t>
@@ -1678,7 +1678,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -1687,16 +1687,16 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
         <v>57</v>
@@ -1705,31 +1705,31 @@
         <v>58</v>
       </c>
       <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" t="s">
         <v>59</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>60</v>
-      </c>
-      <c r="N3" t="s">
-        <v>61</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
       <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T3" t="s">
         <v>62</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R3" t="s">
-        <v>64</v>
-      </c>
-      <c r="S3" t="s">
-        <v>65</v>
-      </c>
-      <c r="T3" t="s">
-        <v>66</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1744,16 +1744,16 @@
         <v>39</v>
       </c>
       <c r="Y3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="Z3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AA3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AB3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="AC3" t="s">
         <v>51</v>
@@ -1761,13 +1761,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -1776,87 +1776,87 @@
         <v>33</v>
       </c>
       <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" t="s">
         <v>72</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>73</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4" t="s">
+        <v>39</v>
+      </c>
+      <c r="V4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y4" t="s">
         <v>74</v>
       </c>
-      <c r="I4" t="s">
+      <c r="Z4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="s">
         <v>73</v>
       </c>
-      <c r="J4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="AB4" t="s">
         <v>76</v>
       </c>
-      <c r="L4" t="s">
-        <v>77</v>
-      </c>
-      <c r="M4" t="s">
-        <v>78</v>
-      </c>
-      <c r="N4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P4" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>81</v>
-      </c>
-      <c r="R4" t="s">
-        <v>82</v>
-      </c>
-      <c r="S4" t="s">
-        <v>83</v>
-      </c>
-      <c r="T4" t="s">
-        <v>84</v>
-      </c>
-      <c r="U4" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" t="s">
-        <v>39</v>
-      </c>
-      <c r="W4" t="s">
-        <v>39</v>
-      </c>
-      <c r="X4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>88</v>
-      </c>
       <c r="AC4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -1865,31 +1865,31 @@
         <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="L5" t="s">
         <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="N5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="O5" t="s">
         <v>42</v>
@@ -1904,13 +1904,13 @@
         <v>39</v>
       </c>
       <c r="S5" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="T5" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="V5" t="s">
         <v>39</v>
@@ -1922,30 +1922,30 @@
         <v>39</v>
       </c>
       <c r="Y5" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="Z5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="AA5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AB5" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AC5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1954,52 +1954,52 @@
         <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="J6" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="K6" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="L6" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Q6" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="R6" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="T6" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="U6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="V6" t="s">
         <v>39</v>
@@ -2011,30 +2011,30 @@
         <v>39</v>
       </c>
       <c r="Y6" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="Z6" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AA6" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AB6" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="AC6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -2043,34 +2043,34 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="H7" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I7" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="K7" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="O7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P7" t="s">
         <v>39</v>
@@ -2100,16 +2100,16 @@
         <v>39</v>
       </c>
       <c r="Y7" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="Z7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="AA7" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="AB7" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="AC7" t="s">
         <v>39</v>
@@ -2117,13 +2117,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -2132,31 +2132,31 @@
         <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="I8" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="O8" t="s">
         <v>42</v>
@@ -2189,16 +2189,16 @@
         <v>39</v>
       </c>
       <c r="Y8" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="Z8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="AA8" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="AB8" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="AC8" t="s">
         <v>39</v>
@@ -2206,13 +2206,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2221,31 +2221,31 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="I9" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="J9" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="K9" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="N9" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="O9" t="s">
         <v>42</v>
@@ -2278,16 +2278,16 @@
         <v>39</v>
       </c>
       <c r="Y9" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="Z9" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="AA9" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="AB9" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="AC9" t="s">
         <v>39</v>
@@ -2295,13 +2295,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -2310,31 +2310,31 @@
         <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="G10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="H10" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="I10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J10" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>150</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="M10" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="N10" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
@@ -2367,16 +2367,16 @@
         <v>39</v>
       </c>
       <c r="Y10" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="Z10" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="AA10" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="AB10" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="AC10" t="s">
         <v>39</v>
@@ -2384,13 +2384,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C11" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -2399,43 +2399,43 @@
         <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G11" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="H11" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="I11" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="K11" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="L11" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="M11" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="N11" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
       <c r="Q11" t="s">
-        <v>178</v>
+        <v>39</v>
       </c>
       <c r="R11" t="s">
-        <v>179</v>
+        <v>39</v>
       </c>
       <c r="S11" t="s">
         <v>39</v>
@@ -2456,16 +2456,16 @@
         <v>39</v>
       </c>
       <c r="Y11" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="Z11" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="AA11" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="AB11" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="AC11" t="s">
         <v>39</v>
@@ -2473,13 +2473,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -2488,53 +2488,53 @@
         <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="I12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="L12" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="M12" t="s">
-        <v>191</v>
+        <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="O12" t="s">
+        <v>39</v>
+      </c>
+      <c r="P12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" t="s">
+        <v>39</v>
+      </c>
+      <c r="S12" t="s">
+        <v>180</v>
+      </c>
+      <c r="T12" t="s">
+        <v>181</v>
+      </c>
+      <c r="U12" t="s">
         <v>42</v>
       </c>
-      <c r="P12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>39</v>
-      </c>
-      <c r="R12" t="s">
-        <v>39</v>
-      </c>
-      <c r="S12" t="s">
-        <v>39</v>
-      </c>
-      <c r="T12" t="s">
-        <v>39</v>
-      </c>
-      <c r="U12" t="s">
-        <v>39</v>
-      </c>
       <c r="V12" t="s">
         <v>39</v>
       </c>
@@ -2545,30 +2545,30 @@
         <v>39</v>
       </c>
       <c r="Y12" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="Z12" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AA12" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AB12" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="AC12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
@@ -2577,43 +2577,43 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="G13" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="H13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="I13" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="J13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="K13" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="L13" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="M13" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="N13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="O13" t="s">
         <v>42</v>
       </c>
       <c r="P13" t="s">
-        <v>206</v>
+        <v>39</v>
       </c>
       <c r="Q13" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="R13" t="s">
-        <v>208</v>
+        <v>39</v>
       </c>
       <c r="S13" t="s">
         <v>39</v>
@@ -2634,16 +2634,16 @@
         <v>39</v>
       </c>
       <c r="Y13" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="Z13" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="AA13" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AB13" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="AC13" t="s">
         <v>39</v>
@@ -2651,13 +2651,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="D14" t="s">
         <v>32</v>
@@ -2666,31 +2666,31 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="H14" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="I14" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>204</v>
       </c>
       <c r="K14" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="L14" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="M14" t="s">
-        <v>60</v>
+        <v>207</v>
       </c>
       <c r="N14" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="O14" t="s">
         <v>42</v>
@@ -2705,13 +2705,13 @@
         <v>39</v>
       </c>
       <c r="S14" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="T14" t="s">
-        <v>39</v>
+        <v>209</v>
       </c>
       <c r="U14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V14" t="s">
         <v>39</v>
@@ -2723,30 +2723,30 @@
         <v>39</v>
       </c>
       <c r="Y14" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="Z14" t="s">
-        <v>68</v>
+        <v>211</v>
       </c>
       <c r="AA14" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="AB14" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AC14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
         <v>32</v>
@@ -2755,52 +2755,52 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G15" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="H15" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="I15" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="J15" t="s">
-        <v>227</v>
+        <v>123</v>
       </c>
       <c r="K15" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="L15" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M15" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
       <c r="N15" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="O15" t="s">
         <v>42</v>
       </c>
       <c r="P15" t="s">
-        <v>39</v>
+        <v>222</v>
       </c>
       <c r="Q15" t="s">
-        <v>39</v>
+        <v>223</v>
       </c>
       <c r="R15" t="s">
-        <v>39</v>
+        <v>224</v>
       </c>
       <c r="S15" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="T15" t="s">
-        <v>39</v>
+        <v>225</v>
       </c>
       <c r="U15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V15" t="s">
         <v>39</v>
@@ -2812,30 +2812,30 @@
         <v>39</v>
       </c>
       <c r="Y15" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="Z15" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="AA15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="AB15" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AC15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
         <v>32</v>
@@ -2844,52 +2844,52 @@
         <v>33</v>
       </c>
       <c r="F16" t="s">
+        <v>230</v>
+      </c>
+      <c r="G16" t="s">
+        <v>231</v>
+      </c>
+      <c r="H16" t="s">
+        <v>232</v>
+      </c>
+      <c r="I16" t="s">
+        <v>231</v>
+      </c>
+      <c r="J16" t="s">
+        <v>233</v>
+      </c>
+      <c r="K16" t="s">
+        <v>234</v>
+      </c>
+      <c r="L16" t="s">
+        <v>235</v>
+      </c>
+      <c r="M16" t="s">
+        <v>236</v>
+      </c>
+      <c r="N16" t="s">
         <v>237</v>
-      </c>
-      <c r="G16" t="s">
-        <v>238</v>
-      </c>
-      <c r="H16" t="s">
-        <v>239</v>
-      </c>
-      <c r="I16" t="s">
-        <v>238</v>
-      </c>
-      <c r="J16" t="s">
-        <v>240</v>
-      </c>
-      <c r="K16" t="s">
-        <v>241</v>
-      </c>
-      <c r="L16" t="s">
-        <v>242</v>
-      </c>
-      <c r="M16" t="s">
-        <v>243</v>
-      </c>
-      <c r="N16" t="s">
-        <v>244</v>
       </c>
       <c r="O16" t="s">
         <v>42</v>
       </c>
       <c r="P16" t="s">
-        <v>39</v>
+        <v>238</v>
       </c>
       <c r="Q16" t="s">
-        <v>39</v>
+        <v>239</v>
       </c>
       <c r="R16" t="s">
-        <v>39</v>
+        <v>240</v>
       </c>
       <c r="S16" t="s">
-        <v>39</v>
+        <v>241</v>
       </c>
       <c r="T16" t="s">
-        <v>39</v>
+        <v>242</v>
       </c>
       <c r="U16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V16" t="s">
         <v>39</v>
@@ -2901,30 +2901,30 @@
         <v>39</v>
       </c>
       <c r="Y16" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA16" t="s">
         <v>245</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AB16" t="s">
         <v>246</v>
       </c>
-      <c r="AA16" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>247</v>
-      </c>
       <c r="AC16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" t="s">
         <v>248</v>
       </c>
-      <c r="B17" t="s">
-        <v>249</v>
-      </c>
       <c r="C17" t="s">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="D17" t="s">
         <v>32</v>
@@ -2933,52 +2933,52 @@
         <v>33</v>
       </c>
       <c r="F17" t="s">
+        <v>249</v>
+      </c>
+      <c r="G17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H17" t="s">
         <v>251</v>
       </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
+        <v>250</v>
+      </c>
+      <c r="J17" t="s">
         <v>252</v>
       </c>
-      <c r="H17" t="s">
+      <c r="K17" t="s">
         <v>253</v>
       </c>
-      <c r="I17" t="s">
-        <v>252</v>
-      </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
         <v>254</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
         <v>255</v>
       </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
         <v>256</v>
-      </c>
-      <c r="M17" t="s">
-        <v>257</v>
-      </c>
-      <c r="N17" t="s">
-        <v>258</v>
       </c>
       <c r="O17" t="s">
         <v>42</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>257</v>
       </c>
       <c r="Q17" t="s">
-        <v>39</v>
+        <v>258</v>
       </c>
       <c r="R17" t="s">
-        <v>39</v>
+        <v>259</v>
       </c>
       <c r="S17" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="T17" t="s">
-        <v>39</v>
+        <v>260</v>
       </c>
       <c r="U17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V17" t="s">
         <v>39</v>
@@ -2990,30 +2990,30 @@
         <v>39</v>
       </c>
       <c r="Y17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Z17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AA17" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AB17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AC17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B18" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
         <v>32</v>
@@ -3022,34 +3022,34 @@
         <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>264</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H18" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I18" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J18" t="s">
-        <v>267</v>
+        <v>39</v>
       </c>
       <c r="K18" t="s">
-        <v>268</v>
+        <v>39</v>
       </c>
       <c r="L18" t="s">
-        <v>269</v>
+        <v>39</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>270</v>
       </c>
       <c r="N18" t="s">
-        <v>39</v>
+        <v>271</v>
       </c>
       <c r="O18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P18" t="s">
         <v>39</v>
@@ -3061,13 +3061,13 @@
         <v>39</v>
       </c>
       <c r="S18" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="T18" t="s">
-        <v>270</v>
+        <v>39</v>
       </c>
       <c r="U18" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="V18" t="s">
         <v>39</v>
@@ -3079,30 +3079,30 @@
         <v>39</v>
       </c>
       <c r="Y18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AA18" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="AB18" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="AC18" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B19" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>32</v>
@@ -3111,31 +3111,31 @@
         <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H19" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="J19" t="s">
-        <v>278</v>
+        <v>39</v>
       </c>
       <c r="K19" t="s">
-        <v>279</v>
+        <v>39</v>
       </c>
       <c r="L19" t="s">
-        <v>208</v>
+        <v>39</v>
       </c>
       <c r="M19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O19" t="s">
         <v>42</v>
@@ -3168,16 +3168,16 @@
         <v>39</v>
       </c>
       <c r="Y19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AB19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AC19" t="s">
         <v>39</v>
@@ -3185,13 +3185,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>288</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -3230,22 +3230,22 @@
         <v>42</v>
       </c>
       <c r="P20" t="s">
-        <v>39</v>
+        <v>297</v>
       </c>
       <c r="Q20" t="s">
-        <v>39</v>
+        <v>298</v>
       </c>
       <c r="R20" t="s">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="S20" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="T20" t="s">
-        <v>297</v>
+        <v>39</v>
       </c>
       <c r="U20" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="V20" t="s">
         <v>39</v>
@@ -3257,19 +3257,19 @@
         <v>39</v>
       </c>
       <c r="Y20" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA20" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="AB20" t="s">
         <v>301</v>
       </c>
       <c r="AC20" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -3414,7 +3414,7 @@
         <v>326</v>
       </c>
       <c r="R22" t="s">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="S22" t="s">
         <v>39</v>
@@ -3497,13 +3497,13 @@
         <v>42</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="Q23" t="s">
         <v>339</v>
       </c>
       <c r="R23" t="s">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="S23" t="s">
         <v>340</v>
@@ -3595,7 +3595,7 @@
         <v>39</v>
       </c>
       <c r="S24" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="T24" t="s">
         <v>356</v>
@@ -3684,7 +3684,7 @@
         <v>39</v>
       </c>
       <c r="S25" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="T25" t="s">
         <v>356</v>
@@ -3725,7 +3725,7 @@
         <v>369</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
         <v>32</v>
@@ -3903,7 +3903,7 @@
         <v>397</v>
       </c>
       <c r="C28" t="s">
-        <v>250</v>
+        <v>159</v>
       </c>
       <c r="D28" t="s">
         <v>32</v>
@@ -3992,7 +3992,7 @@
         <v>410</v>
       </c>
       <c r="C29" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="D29" t="s">
         <v>32</v>
@@ -4040,7 +4040,7 @@
         <v>324</v>
       </c>
       <c r="S29" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="T29" t="s">
         <v>421</v>
@@ -4081,7 +4081,7 @@
         <v>426</v>
       </c>
       <c r="C30" t="s">
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -4129,7 +4129,7 @@
         <v>39</v>
       </c>
       <c r="S30" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="T30" t="s">
         <v>435</v>
@@ -4348,7 +4348,7 @@
         <v>457</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
         <v>32</v>
@@ -4360,13 +4360,13 @@
         <v>458</v>
       </c>
       <c r="G33" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="H33" t="s">
         <v>459</v>
       </c>
       <c r="I33" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="J33" t="s">
         <v>39</v>
@@ -4437,7 +4437,7 @@
         <v>461</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
         <v>32</v>
@@ -4526,7 +4526,7 @@
         <v>466</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>267</v>
       </c>
       <c r="D35" t="s">
         <v>32</v>
